--- a/results/Int Task Remove ACC -0.8/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_2_permute.xlsx
@@ -440,837 +440,837 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6824646899065147</v>
+        <v>0.701832529270898</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6787006653587562</v>
+        <v>0.6979700623468383</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6784901662349632</v>
+        <v>0.6912511956210596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.669857607640804</v>
+        <v>0.632757224343892</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6679767298978574</v>
+        <v>0.6378781478869797</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6437380874252082</v>
+        <v>0.6387484203838554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6377378151377844</v>
+        <v>0.6383625053235682</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6282632600484532</v>
+        <v>0.6344626861503446</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6427512200571106</v>
+        <v>0.6340247572103804</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6380841088870426</v>
+        <v>0.6558302671907618</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.641635365249143</v>
+        <v>0.6210012148208139</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.647104851603354</v>
+        <v>0.637961928632768</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6495142462176484</v>
+        <v>0.6417236841186614</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6895298503815515</v>
+        <v>0.6512752127681856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7029393078314052</v>
+        <v>0.6631455481006208</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7035662670790541</v>
+        <v>0.6869586542019535</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7033229538298273</v>
+        <v>0.6988165969657406</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6978161152264524</v>
+        <v>0.6786769274807828</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6992126355328105</v>
+        <v>0.6920931921162319</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6977482179137198</v>
+        <v>0.6920931921162319</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7009814565282655</v>
+        <v>0.6842357799638347</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7019218953997388</v>
+        <v>0.6869122257053292</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7189946659591848</v>
+        <v>0.6526197191948671</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7078169181252663</v>
+        <v>0.6527928660694962</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7236289630038191</v>
+        <v>0.6487130928360481</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7554307377592839</v>
+        <v>0.6398518826231752</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7565465925672515</v>
+        <v>0.676908106485328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7720123436965461</v>
+        <v>0.6946825407907506</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7639625849152767</v>
+        <v>0.6931128736097631</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7697851722043413</v>
+        <v>0.6940204983558029</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7560294210052294</v>
+        <v>0.6731781178655458</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7532126425145395</v>
+        <v>0.7153439199614609</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7502204480873553</v>
+        <v>0.7173391235137645</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7505293895874496</v>
+        <v>0.7173742067010633</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7756575043112175</v>
+        <v>0.7144431024010165</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7636286837346664</v>
+        <v>0.7203290488790834</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.767947232093611</v>
+        <v>0.6963213270870132</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.767947232093611</v>
+        <v>0.6982180882630157</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7671799400967667</v>
+        <v>0.6982577095740448</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7606975794346196</v>
+        <v>0.6791954953885682</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7766635714335584</v>
+        <v>0.6728274605357779</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7737879718775964</v>
+        <v>0.6793663732013321</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7828788809685054</v>
+        <v>0.6908553315972101</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7828788809685054</v>
+        <v>0.6987205981945249</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7854546152718336</v>
+        <v>0.7513443318834609</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7896406853265006</v>
+        <v>0.7503415810823075</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7921530604408265</v>
+        <v>0.7503415810823075</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7921530604408265</v>
+        <v>0.7458498858487339</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7915589153186111</v>
+        <v>0.7115402741026733</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7836891105975662</v>
+        <v>0.587612144019102</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7723586374458044</v>
+        <v>0.5947825540560353</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7578989534388505</v>
+        <v>0.5928337790003561</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7322367364606823</v>
+        <v>0.5952555661832983</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7229772186188743</v>
+        <v>0.6049971723998296</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7200857356298567</v>
+        <v>0.557806620075263</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.715977686394705</v>
+        <v>0.6043250064580992</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6780918586060281</v>
+        <v>0.5676978098316705</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6785784851044816</v>
+        <v>0.5679762062681961</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6817438264062947</v>
+        <v>0.5695786875746173</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6424220315434508</v>
+        <v>0.5674567656443088</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6583901180610343</v>
+        <v>0.5674567656443088</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6901103811325761</v>
+        <v>0.5815497343452186</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7050860148990092</v>
+        <v>0.5821416104055687</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7041728047699172</v>
+        <v>0.5465091355921553</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6749944146169475</v>
+        <v>0.5484647178334299</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7159570902946988</v>
+        <v>0.5424101626044642</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7302923249855129</v>
+        <v>0.5355204180659214</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.732882720919354</v>
+        <v>0.6145453847281663</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7329857014193855</v>
+        <v>0.6337173865992698</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7329857014193855</v>
+        <v>0.6430425326919452</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.732461722671768</v>
+        <v>0.6359445580914747</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.732461722671768</v>
+        <v>0.6359445580914747</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7330185155448192</v>
+        <v>0.6169830553441643</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7344365046672857</v>
+        <v>0.6101283939929205</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7368527064671755</v>
+        <v>0.5210155273648861</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.714913670923194</v>
+        <v>0.5086981868450265</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7160996921057592</v>
+        <v>0.5086981868450265</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6852881010395794</v>
+        <v>0.5137093227024876</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6852881010395794</v>
+        <v>0.5105439814006745</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6706372922062962</v>
+        <v>0.5084548735957998</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6778157312313675</v>
+        <v>0.501391982182628</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6762460640503801</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6731213913189185</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6641800657678855</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
@@ -1280,47 +1280,47 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6647368586409367</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6074437447200676</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.593045150840251</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5010816443367707</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4996737787210869</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
